--- a/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/Town.xlsx
+++ b/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/Town.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLab\REDIV\ReDiv_Online\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22F61D61-CFCF-4FD7-B49D-7F8A0C37BA59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7953327-FBF9-4E54-BEF8-EB6038A623DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="5040" windowWidth="47520" windowHeight="15840" xr2:uid="{B74E668D-3D54-4994-8BA3-4C053C68EB4C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="29">
   <si>
     <t>##var</t>
   </si>
@@ -119,7 +119,14 @@
     <t>兰德索尔</t>
   </si>
   <si>
-    <t/>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UIBackground/Town/50020/Town_500020.prefab</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UIBackground/Town/50020/Town_500022.prefab</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UIBackground/Town/50020/Town_500021.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -506,6 +513,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76A1B28C-0EB8-496B-9379-130E46DC4D4C}">
   <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="23.1640625" customWidth="1"/>
+    <col min="3" max="3" width="56.6640625" customWidth="1"/>
+    <col min="4" max="4" width="26.6640625" customWidth="1"/>
+    <col min="5" max="5" width="23.1640625" customWidth="1"/>
+    <col min="6" max="6" width="21.33203125" customWidth="1"/>
+    <col min="7" max="7" width="28.75" customWidth="1"/>
+    <col min="8" max="8" width="26.1640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -628,10 +644,10 @@
         <v>26</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/Town.xlsx
+++ b/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/Town.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLab\REDIV\ReDiv_Online\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7953327-FBF9-4E54-BEF8-EB6038A623DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7372DD64-F983-40D6-B719-93A58468C754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="5040" windowWidth="47520" windowHeight="15840" xr2:uid="{B74E668D-3D54-4994-8BA3-4C053C68EB4C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{B74E668D-3D54-4994-8BA3-4C053C68EB4C}"/>
   </bookViews>
   <sheets>
     <sheet name="Town" sheetId="1" r:id="rId1"/>
@@ -119,13 +119,15 @@
     <t>兰德索尔</t>
   </si>
   <si>
-    <t>Assets/AddressableAssets/Remote/Prefabs/UIBackground/Town/50020/Town_500020.prefab</t>
-  </si>
-  <si>
-    <t>Assets/AddressableAssets/Remote/Prefabs/UIBackground/Town/50020/Town_500022.prefab</t>
-  </si>
-  <si>
-    <t>Assets/AddressableAssets/Remote/Prefabs/UIBackground/Town/50020/Town_500021.prefab</t>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UIBackground/Town/50020/Town_50020.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UIBackground/Town/50020/Town_50021.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/UIBackground/Town/50020/Town_50022.prefab</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -644,10 +646,10 @@
         <v>26</v>
       </c>
       <c r="G5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/Town.xlsx
+++ b/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/Town.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLab\REDIV\ReDiv_Online\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7372DD64-F983-40D6-B719-93A58468C754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDB180BD-DE89-4F56-BA9D-F460B224E91A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{B74E668D-3D54-4994-8BA3-4C053C68EB4C}"/>
   </bookViews>
@@ -119,15 +119,15 @@
     <t>兰德索尔</t>
   </si>
   <si>
-    <t>Assets/AddressableAssets/Remote/Prefabs/UIBackground/Town/50020/Town_50020.prefab</t>
+    <t>Assets/AddressableAssets/Remote/Prefabs/Town/50020/Town_50020.prefab</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Assets/AddressableAssets/Remote/Prefabs/UIBackground/Town/50020/Town_50021.prefab</t>
+    <t>Assets/AddressableAssets/Remote/Prefabs/Town/50020/Town_50021.prefab</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Assets/AddressableAssets/Remote/Prefabs/UIBackground/Town/50020/Town_50022.prefab</t>
+    <t>Assets/AddressableAssets/Remote/Prefabs/Town/50020/Town_50022.prefab</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/Town.xlsx
+++ b/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/Town.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLab\REDIV\ReDiv_Online\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDB180BD-DE89-4F56-BA9D-F460B224E91A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DEDED3E-340E-4016-9C04-7689B2B748F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{B74E668D-3D54-4994-8BA3-4C053C68EB4C}"/>
+    <workbookView xWindow="0" yWindow="5040" windowWidth="51320" windowHeight="15840" xr2:uid="{B74E668D-3D54-4994-8BA3-4C053C68EB4C}"/>
   </bookViews>
   <sheets>
     <sheet name="Town" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
   <si>
     <t>##var</t>
   </si>
@@ -129,6 +129,21 @@
   <si>
     <t>Assets/AddressableAssets/Remote/Prefabs/Town/50020/Town_50022.prefab</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>False</t>
+  </si>
+  <si>
+    <t>测试镇</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/Town/50020/Town_50020.prefab</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/Town/50020/Town_50021.prefab</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/Town/50020/Town_50022.prefab</t>
   </si>
 </sst>
 </file>
@@ -513,7 +528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76A1B28C-0EB8-496B-9379-130E46DC4D4C}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="23.1640625" customWidth="1"/>
@@ -652,6 +667,29 @@
         <v>28</v>
       </c>
     </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
